--- a/restoration-calculator/templates/seisan_template.xlsx
+++ b/restoration-calculator/templates/seisan_template.xlsx
@@ -86,7 +86,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -459,12 +459,12 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,7 +507,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>工事・部材名</t>
@@ -552,6 +552,6 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>